--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484743_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484743_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8025</v>
+        <v>6.0986</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4017</v>
+        <v>4.4862</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4008</v>
+        <v>1.6124</v>
       </c>
       <c r="G2" t="n">
         <v>3.9797</v>
@@ -610,13 +610,13 @@
         <v>3.2079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7471</v>
+        <v>0.0432</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2585</v>
+        <v>0.3429</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5114</v>
+        <v>-0.2997</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1583</v>
+        <v>1.8635</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2393</v>
+        <v>0.1032</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9191</v>
+        <v>1.7604</v>
       </c>
       <c r="G3" t="n">
         <v>1.7475</v>
@@ -688,13 +688,13 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.0161</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0617</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.783</v>
+        <v>-0.9417</v>
       </c>
       <c r="V3" t="n">
         <v>0.9434</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0208</v>
+        <v>1.8054</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.6325</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2522</v>
+        <v>1.1729</v>
       </c>
       <c r="G4" t="n">
         <v>0.6985</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6778</v>
+        <v>-0.8932</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0436</v>
+        <v>-0.1796</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6342</v>
+        <v>-0.7136</v>
       </c>
       <c r="V4" t="n">
         <v>0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8829</v>
+        <v>1.546</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7906</v>
+        <v>1.4466</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6735</v>
+        <v>0.0994</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4358</v>
+        <v>2.6426</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5159</v>
+        <v>1.4282</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9199000000000001</v>
+        <v>1.2143</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5685</v>
+        <v>2.4544</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1246</v>
+        <v>1.7381</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4439</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8673</v>
+        <v>0.1882</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3913</v>
+        <v>-0.3099</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.476</v>
+        <v>0.4981</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2644</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7901</v>
+        <v>-0.5305</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4761</v>
+        <v>0.2566</v>
       </c>
       <c r="U5" t="n">
-        <v>0.314</v>
+        <v>-0.7871</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2642</v>
+        <v>-0.9434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3018</v>
+        <v>-0.3208</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9624</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2395</v>
+        <v>1.4764</v>
       </c>
       <c r="E6" t="n">
-        <v>1.193</v>
+        <v>-0.9855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0465</v>
+        <v>2.4618</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6426</v>
+        <v>-2.4358</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4282</v>
+        <v>-1.5159</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2143</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4544</v>
+        <v>-1.5685</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7381</v>
+        <v>-1.1246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.4439</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1882</v>
+        <v>-0.8673</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3099</v>
+        <v>-0.3913</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4981</v>
+        <v>-0.476</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>2.2644</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>2.2644</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8371</v>
+        <v>0.3836</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0029</v>
+        <v>0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.84</v>
+        <v>0.1023</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9434</v>
+        <v>1.2642</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6226</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1544</v>
+        <v>0.3422</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7681</v>
+        <v>-0.1256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9225</v>
+        <v>0.4679</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4411</v>
+        <v>2.1928</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8916</v>
+        <v>2.1928</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4504</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3695</v>
+        <v>2.0278</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4518</v>
+        <v>3.1538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0823</v>
+        <v>-1.1261</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0716</v>
+        <v>0.1651</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4398</v>
+        <v>-0.961</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3682</v>
+        <v>1.1261</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R7" t="n">
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2557</v>
+        <v>-1.4167</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2997</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.044</v>
+        <v>-1.339</v>
       </c>
       <c r="V7" t="n">
-        <v>0.019</v>
+        <v>-0.6226</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2262</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0005</v>
+        <v>-0.2088</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-1.1578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5737</v>
+        <v>0.9489</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1928</v>
+        <v>-1.4411</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1928</v>
+        <v>-1.8916</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0.4504</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0278</v>
+        <v>-1.3695</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1538</v>
+        <v>-1.4518</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1261</v>
+        <v>0.0823</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1651</v>
+        <v>-0.0716</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.961</v>
+        <v>-0.4398</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1261</v>
+        <v>0.3682</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
         <v>2.2644</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7594</v>
+        <v>-0.1076</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5262</v>
+        <v>-0.09</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2332</v>
+        <v>-0.0176</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6226</v>
+        <v>0.019</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6226</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4439</v>
+        <v>-0.4418</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6854</v>
+        <v>-0.7627</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2415</v>
+        <v>0.3209</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2051</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0436</v>
+        <v>-0.1208</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8935</v>
+        <v>-0.8141</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6226</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8136</v>
+        <v>-1.7746</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8654</v>
+        <v>-0.7735</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9482</v>
+        <v>-1.0011</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2587</v>
@@ -1234,13 +1234,13 @@
         <v>3.0192</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3097</v>
+        <v>-0.2707</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3398</v>
+        <v>-0.2479</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0301</v>
+        <v>-0.0229</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2452</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3833</v>
+        <v>-6.5018</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6333</v>
+        <v>-7.9899</v>
       </c>
       <c r="F11" t="n">
-        <v>1.25</v>
+        <v>1.4881</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9474</v>
@@ -1312,13 +1312,13 @@
         <v>3.0192</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7377</v>
+        <v>-0.8562</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3398</v>
+        <v>-0.6964</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3979</v>
+        <v>-0.1598</v>
       </c>
       <c r="V11" t="n">
         <v>0.3018</v>
@@ -1345,43 +1345,43 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.617099999999999</v>
+        <v>4.205100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.714300000000001</v>
+        <v>-5.1265</v>
       </c>
       <c r="F12" t="n">
         <v>9.3316</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9729999999999999</v>
+        <v>0.9730000000000008</v>
       </c>
       <c r="H12" t="n">
         <v>-1.9488</v>
       </c>
       <c r="I12" t="n">
-        <v>2.921599999999999</v>
+        <v>2.921599999999998</v>
       </c>
       <c r="J12" t="n">
         <v>4.047599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1848</v>
+        <v>3.184800000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8624999999999994</v>
+        <v>0.8625000000000003</v>
       </c>
       <c r="M12" t="n">
         <v>-3.0745</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.133699999999999</v>
+        <v>-5.1337</v>
       </c>
       <c r="O12" t="n">
         <v>2.0591</v>
       </c>
       <c r="P12" t="n">
-        <v>9.435</v>
+        <v>9.434999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.2655</v>
@@ -1390,22 +1390,22 @@
         <v>21.7005</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.1871</v>
+        <v>-5.599200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1941</v>
+        <v>-0.6061000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.9931</v>
+        <v>-4.9932</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6035999999999997</v>
+        <v>-0.6036000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>3.6976</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.301200000000001</v>
+        <v>-4.3012</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1341</v>
+        <v>2.1055</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4563</v>
+        <v>1.1897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6778</v>
+        <v>0.9159</v>
       </c>
       <c r="G13" t="n">
         <v>0.0871</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9827</v>
+        <v>1.9541</v>
       </c>
       <c r="T13" t="n">
-        <v>2.734</v>
+        <v>1.4673</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2487</v>
+        <v>0.4868</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8792</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6751</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7039</v>
+        <v>-0.6273</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0288</v>
+        <v>1.4141</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.175</v>
+        <v>0.3293</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.015</v>
+        <v>1.0526</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.16</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.06900000000000001</v>
+        <v>1.2844</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1683</v>
+        <v>1.3155</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0993</v>
+        <v>-0.0311</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.106</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8467</v>
+        <v>-0.2629</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2593</v>
+        <v>-0.6922</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6983</v>
+        <v>-4.3401</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1887</v>
+        <v>-6.6045</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6989</v>
+        <v>0.696</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9616</v>
+        <v>0.6554</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7372</v>
+        <v>0.0407</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.547</v>
+        <v>4.1016</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.0374</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.547</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.271</v>
+        <v>0.3239</v>
       </c>
       <c r="E15" t="n">
         <v>0.0211</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2499</v>
+        <v>0.3028</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1416</v>
@@ -1624,13 +1624,13 @@
         <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0224</v>
+        <v>0.2784</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7925</v>
+        <v>0.4242</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8149</v>
+        <v>-0.1458</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5779</v>
+        <v>-0.4833</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1604</v>
+        <v>-0.2019</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7383</v>
+        <v>-0.2814</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1946</v>
+        <v>0.0423</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0634</v>
+        <v>0.0423</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.258</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6167</v>
+        <v>-0.5256</v>
       </c>
       <c r="N16" t="n">
-        <v>0.097</v>
+        <v>-0.2442</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5196</v>
+        <v>-0.2814</v>
       </c>
       <c r="P16" t="n">
         <v>0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3474</v>
+        <v>0.573</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5908</v>
+        <v>0.3819</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2433</v>
+        <v>0.1911</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2881</v>
+        <v>0.1796</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.063</v>
+        <v>0.3142</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2252</v>
+        <v>-0.1346</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4833</v>
+        <v>-1.175</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2019</v>
+        <v>-1.015</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2814</v>
+        <v>-0.16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0423</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0423</v>
+        <v>-0.1683</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0993</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5256</v>
+        <v>-1.106</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2442</v>
+        <v>-0.8467</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2814</v>
+        <v>-0.2593</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0065</v>
+        <v>1.2033</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1052</v>
+        <v>0.5719</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1117</v>
+        <v>0.6314</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6353</v>
+        <v>-0.2964</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1856</v>
+        <v>-1.0848</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5503</v>
+        <v>0.7885</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.874</v>
+        <v>-0.5779</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.497</v>
+        <v>0.1604</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.377</v>
+        <v>-0.7383</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.369</v>
+        <v>-1.1946</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5111</v>
+        <v>0.0634</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8579</v>
+        <v>-1.258</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.505</v>
+        <v>0.6167</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0141</v>
+        <v>0.097</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5191</v>
+        <v>0.5196</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2691</v>
+        <v>0.0287</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7876</v>
+        <v>0.2985</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4816</v>
+        <v>-0.2698</v>
       </c>
       <c r="V18" t="n">
-        <v>0.347</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0.06419999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8384</v>
+        <v>-0.4342</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0256</v>
+        <v>-0.8307</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1872</v>
+        <v>0.3965</v>
       </c>
       <c r="G19" t="n">
         <v>0.0623</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0994</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0058</v>
+        <v>0.2007</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0936</v>
+        <v>0.3028</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6226</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1472</v>
+        <v>-1.1728</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7965</v>
+        <v>-0.0718</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6493</v>
+        <v>-1.101</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3293</v>
+        <v>1.2511</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0526</v>
+        <v>1.6669</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4158</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2844</v>
+        <v>1.0845</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3155</v>
+        <v>1.717</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0311</v>
+        <v>-0.6325</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.1666</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2629</v>
+        <v>-0.0501</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6922</v>
+        <v>0.2167</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.3401</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.6045</v>
+        <v>-2.0757</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.238</v>
+        <v>-0.0541</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5139</v>
+        <v>0.2968</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7242</v>
+        <v>-0.3509</v>
       </c>
       <c r="V20" t="n">
-        <v>4.1016</v>
+        <v>-0.8603</v>
       </c>
       <c r="W20" t="n">
-        <v>4.0374</v>
+        <v>0.6226</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06419999999999999</v>
+        <v>-1.4829</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4614</v>
+        <v>-1.6817</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0718</v>
+        <v>-2.9651</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3897</v>
+        <v>1.2834</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2511</v>
+        <v>-2.874</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6669</v>
+        <v>-0.497</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4158</v>
+        <v>-2.377</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0845</v>
+        <v>-2.369</v>
       </c>
       <c r="K21" t="n">
-        <v>1.717</v>
+        <v>-0.5111</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6325</v>
+        <v>-1.8579</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1666</v>
+        <v>-0.505</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0501</v>
+        <v>0.0141</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2167</v>
+        <v>-0.5191</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5096</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3427</v>
+        <v>1.2227</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2968</v>
+        <v>1.0081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6395</v>
+        <v>0.2147</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8603</v>
+        <v>0.347</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6226</v>
+        <v>0.2828</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4829</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3493</v>
+        <v>-3.0568</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5778</v>
+        <v>-5.7009</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2285</v>
+        <v>2.6441</v>
       </c>
       <c r="G22" t="n">
         <v>2.549</v>
@@ -2170,13 +2170,13 @@
         <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3287</v>
+        <v>0.6213</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7642</v>
+        <v>0.1127</v>
       </c>
       <c r="U22" t="n">
-        <v>1.093</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6171</v>
+        <v>-2.9677</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.3315</v>
+        <v>-9.331399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>5.7142</v>
+        <v>6.3639</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9730000000000003</v>
+        <v>-0.9729999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>1.9485</v>
@@ -2224,7 +2224,7 @@
         <v>3.0745</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1336</v>
+        <v>5.133599999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-2.0591</v>
@@ -2233,10 +2233,10 @@
         <v>-4.0476</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.185099999999999</v>
+        <v>-3.1851</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8626000000000004</v>
+        <v>-0.8625999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-9.434999999999999</v>
@@ -2248,16 +2248,16 @@
         <v>12.2655</v>
       </c>
       <c r="S23" t="n">
-        <v>6.187299999999999</v>
+        <v>6.8367</v>
       </c>
       <c r="T23" t="n">
         <v>4.9933</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1941</v>
+        <v>1.8436</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6037000000000005</v>
+        <v>0.6037000000000003</v>
       </c>
       <c r="W23" t="n">
         <v>4.3012</v>
